--- a/ig/DM-FEVRIER-2026/CodeSystem-TRE-R58-AutreTypeDiplome.xlsx
+++ b/ig/DM-FEVRIER-2026/CodeSystem-TRE-R58-AutreTypeDiplome.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260223120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-23T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -727,7 +727,7 @@
     <t>DIP356</t>
   </si>
   <si>
-    <t>Licence + Maîtrise + DESS en psychologie</t>
+    <t>Licence psychologie + Maîtrise psychologie + DESS en psychologie</t>
   </si>
   <si>
     <t>Article 44 de la Loi n° 85-772 du 25 juillet 1985 et article 1er du décret n°90-255 du 22 mars 1990</t>
@@ -736,22 +736,22 @@
     <t>DIP357</t>
   </si>
   <si>
-    <t>Licence + Maîtrise + diplôme annexe Décret 90-255</t>
+    <t>Licence psychologie + Maîtrise psychologie + diplôme annexe Décret 90-255</t>
+  </si>
+  <si>
+    <t>DIP358</t>
+  </si>
+  <si>
+    <t>Licence psychologie + Maîtrise psychologie + DEA psychologie + Attestation Stage</t>
+  </si>
+  <si>
+    <t>DIP359</t>
+  </si>
+  <si>
+    <t>Diplôme pour usage du titre de psychologue (alinéa 6 à 9 art 1 décret 90-255)</t>
   </si>
   <si>
     <t>Article 44 de la loi n° 85-772 du 25 juillet 1985 et article 1er du décret n°90-255 du 22 mars 1990</t>
-  </si>
-  <si>
-    <t>DIP358</t>
-  </si>
-  <si>
-    <t>Licence psychologie + Maîtrise psychologie + DEA psychologie + Attestation Stage</t>
-  </si>
-  <si>
-    <t>DIP359</t>
-  </si>
-  <si>
-    <t>Diplôme pour usage du titre de psychologue (alinéa 6 à 9 art 1 décret 90-255)</t>
   </si>
   <si>
     <t>DIP360</t>
@@ -2288,7 +2288,7 @@
         <v>240</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82">
@@ -2296,13 +2296,13 @@
         <v>61</v>
       </c>
       <c r="B82" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C82" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="C82" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="D82" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83">
@@ -2310,13 +2310,13 @@
         <v>61</v>
       </c>
       <c r="B83" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="C83" t="s" s="2">
+      <c r="D83" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>241</v>
       </c>
     </row>
     <row r="84">
